--- a/MAS_Benchmarks.xlsx
+++ b/MAS_Benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02D73E6E-9925-47AD-ACA6-00C4A3F49662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94F6D4DC-B64C-4ECD-817A-E6EC2C15A2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1390" yWindow="80" windowWidth="34320" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="140" windowWidth="32730" windowHeight="13040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark_Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
   <si>
     <t>ManagerTeam</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>Seshu Chivukula</t>
-  </si>
-  <si>
-    <t>Willery Rivers</t>
   </si>
   <si>
     <t>Connie Serrano</t>
@@ -218,8 +215,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:E15" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E15" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:E14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E14" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{184B8945-C042-4F94-9625-44B9911492BE}" name="ManagerTeam" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{F39D70CE-E74D-40F2-80E4-9FA1AF055671}" name="Associate Name" dataDxfId="3"/>
@@ -528,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
@@ -553,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -561,7 +558,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
@@ -570,7 +567,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -578,7 +575,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>97.5</v>
@@ -587,7 +584,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -595,7 +592,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>85.56</v>
@@ -604,7 +601,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -612,7 +609,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>80.709999999999994</v>
@@ -621,7 +618,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -638,7 +635,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -646,7 +643,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>76.25</v>
@@ -655,7 +652,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -663,7 +660,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1">
         <v>71.25</v>
@@ -672,24 +669,24 @@
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -697,16 +694,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -714,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -731,13 +728,13 @@
         <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>21</v>
@@ -748,16 +745,16 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -765,33 +762,16 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="1">
-        <v>41</v>
-      </c>
-      <c r="D15" s="1">
-        <v>6</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -803,28 +783,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -1075,32 +1033,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AB7CB68-540E-4F04-820F-834558F23155}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1117,4 +1072,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/MAS_Benchmarks.xlsx
+++ b/MAS_Benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94F6D4DC-B64C-4ECD-817A-E6EC2C15A2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A861A9B-EBB7-4548-8C97-315C676A51EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="140" windowWidth="32730" windowHeight="13040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="30" windowWidth="20210" windowHeight="13490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark_Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>ManagerTeam</t>
   </si>
@@ -47,9 +47,6 @@
     <t>BenchmarkAverageScore</t>
   </si>
   <si>
-    <t>BenchmarkRank</t>
-  </si>
-  <si>
     <t>Charles</t>
   </si>
   <si>
@@ -95,13 +92,10 @@
     <t>Thomas Gordon</t>
   </si>
   <si>
-    <t>BenchmarkGroup</t>
-  </si>
-  <si>
-    <t>Top 20%</t>
-  </si>
-  <si>
-    <t>Bottom 20%</t>
+    <t>TyKee Walmsley</t>
+  </si>
+  <si>
+    <t>Willery Rivers</t>
   </si>
 </sst>
 </file>
@@ -145,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -153,17 +147,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -215,14 +206,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:E14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E14" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{184B8945-C042-4F94-9625-44B9911492BE}" name="ManagerTeam" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{F39D70CE-E74D-40F2-80E4-9FA1AF055671}" name="Associate Name" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{493C204F-90F3-43AF-93C9-1A6906233A17}" name="BenchmarkAverageScore" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{0AB553B9-16C6-453F-B1E2-1B4084C8EF4E}" name="BenchmarkRank" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{3C223DAB-4B57-4152-A6CF-3746484C3D9C}" name="BenchmarkGroup" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:C16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C16" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{184B8945-C042-4F94-9625-44B9911492BE}" name="ManagerTeam" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{F39D70CE-E74D-40F2-80E4-9FA1AF055671}" name="Associate Name" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{493C204F-90F3-43AF-93C9-1A6906233A17}" name="BenchmarkAverageScore" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -525,18 +514,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -546,232 +533,170 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
         <v>100</v>
       </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1">
-        <v>97.5</v>
-      </c>
-      <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+        <v>97.78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>85.56</v>
       </c>
-      <c r="D4" s="1">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1">
+        <v>73.89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>67.78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>74.44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1">
-        <v>80.709999999999994</v>
-      </c>
-      <c r="D5" s="1">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <v>77.78</v>
-      </c>
-      <c r="D6" s="1">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1">
-        <v>76.25</v>
-      </c>
-      <c r="D7" s="1">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1">
-        <v>71.25</v>
-      </c>
-      <c r="D8" s="1">
-        <v>7</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>100</v>
       </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1">
         <v>79</v>
       </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1">
         <v>65</v>
       </c>
-      <c r="D11" s="1">
-        <v>3</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>55</v>
       </c>
-      <c r="D12" s="1">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="1">
         <v>44</v>
       </c>
-      <c r="D13" s="1">
-        <v>5</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1">
         <v>41</v>
       </c>
-      <c r="D14" s="1">
-        <v>6</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>21</v>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>96.67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1">
+        <v>53.64</v>
       </c>
     </row>
   </sheetData>
@@ -783,6 +708,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -1033,15 +967,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1056,6 +981,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AB7CB68-540E-4F04-820F-834558F23155}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1074,14 +1007,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
   <ds:schemaRefs>

--- a/MAS_Benchmarks.xlsx
+++ b/MAS_Benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A861A9B-EBB7-4548-8C97-315C676A51EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD131D0D-AF21-49A3-BDDB-31A70E0D1FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9600" yWindow="30" windowWidth="20210" windowHeight="13490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="190" windowWidth="29960" windowHeight="13490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark_Data" sheetId="1" r:id="rId1"/>
@@ -139,16 +139,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -681,7 +678,7 @@
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="1">
@@ -692,7 +689,7 @@
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="1">
@@ -708,12 +705,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -968,22 +969,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1008,18 +1014,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Benchmarks.xlsx
+++ b/MAS_Benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD131D0D-AF21-49A3-BDDB-31A70E0D1FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A117F-B0BD-45C0-962E-F6D60D29CC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="190" windowWidth="29960" windowHeight="13490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1780" yWindow="370" windowWidth="29960" windowHeight="13490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark_Data" sheetId="1" r:id="rId1"/>
@@ -705,16 +705,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -969,27 +965,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1014,9 +1005,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/MAS_Benchmarks.xlsx
+++ b/MAS_Benchmarks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413A117F-B0BD-45C0-962E-F6D60D29CC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935732B8-2D9D-4CF3-99F5-F70A618E6940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1780" yWindow="370" windowWidth="29960" windowHeight="13490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15180" yWindow="0" windowWidth="19280" windowHeight="13670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark_Data" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="25">
   <si>
     <t>ManagerTeam</t>
-  </si>
-  <si>
-    <t>Associate Name</t>
-  </si>
-  <si>
-    <t>BenchmarkAverageScore</t>
   </si>
   <si>
     <t>Charles</t>
@@ -92,17 +86,38 @@
     <t>Thomas Gordon</t>
   </si>
   <si>
-    <t>TyKee Walmsley</t>
+    <t>Willery Rivers</t>
   </si>
   <si>
-    <t>Willery Rivers</t>
+    <t>AssociateName</t>
+  </si>
+  <si>
+    <t>BenchmarkMonth</t>
+  </si>
+  <si>
+    <t>BenchmarkQuarter</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Tykee Walmsley</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>Janruary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -114,6 +129,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -139,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -147,11 +168,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -203,12 +236,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:C16" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
-  <autoFilter ref="A1:C16" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{184B8945-C042-4F94-9625-44B9911492BE}" name="ManagerTeam" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{F39D70CE-E74D-40F2-80E4-9FA1AF055671}" name="Associate Name" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{493C204F-90F3-43AF-93C9-1A6906233A17}" name="BenchmarkAverageScore" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:E151" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E151" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{184B8945-C042-4F94-9625-44B9911492BE}" name="AssociateName" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{F39D70CE-E74D-40F2-80E4-9FA1AF055671}" name="ManagerTeam" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{493C204F-90F3-43AF-93C9-1A6906233A17}" name="BenchmarkMonth" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{8C343565-A987-4283-AB18-2355E55D6660}" name="BenchmarkQuarter" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{B8DCB57D-BA4A-4AEE-B7C5-15B76BCB3BBE}" name="Score" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -511,192 +546,2585 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" customWidth="1"/>
+    <col min="3" max="3" width="32.6328125" customWidth="1"/>
+    <col min="4" max="4" width="21.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+      <c r="E48" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="E56" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1</v>
+      </c>
+      <c r="E59" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+      <c r="E72" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>21</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="E73" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+      <c r="E74" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
+      </c>
+      <c r="E75" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1</v>
+      </c>
+      <c r="E81" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>16</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1</v>
+      </c>
+      <c r="E83" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D86" s="1">
+        <v>1</v>
+      </c>
+      <c r="E86" s="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" s="1">
+        <v>1</v>
+      </c>
+      <c r="E87" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="1">
+        <v>1</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="1">
+        <v>1</v>
+      </c>
+      <c r="E89" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1</v>
+      </c>
+      <c r="E90" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1</v>
+      </c>
+      <c r="E91" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="1">
+        <v>1</v>
+      </c>
+      <c r="E92" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" s="1">
+        <v>1</v>
+      </c>
+      <c r="E93" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="1">
+        <v>1</v>
+      </c>
+      <c r="E94" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="1">
+        <v>1</v>
+      </c>
+      <c r="E95" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="1">
+        <v>1</v>
+      </c>
+      <c r="E96" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1">
-        <v>97.78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1">
-        <v>85.56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1">
-        <v>73.89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B97" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" s="1">
+        <v>1</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="1">
+        <v>1</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="1">
+        <v>1</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1</v>
+      </c>
+      <c r="E101" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D102" s="1">
+        <v>1</v>
+      </c>
+      <c r="E102" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D103" s="1">
+        <v>1</v>
+      </c>
+      <c r="E103" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1</v>
+      </c>
+      <c r="E104" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D105" s="1">
+        <v>1</v>
+      </c>
+      <c r="E105" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D106" s="1">
+        <v>1</v>
+      </c>
+      <c r="E106" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" s="1">
+        <v>1</v>
+      </c>
+      <c r="E107" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1</v>
+      </c>
+      <c r="E108" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="1">
+        <v>1</v>
+      </c>
+      <c r="E109" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D110" s="1">
+        <v>1</v>
+      </c>
+      <c r="E110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D111" s="1">
+        <v>1</v>
+      </c>
+      <c r="E111" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D112" s="1">
+        <v>1</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D113" s="1">
+        <v>1</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D114" s="1">
+        <v>1</v>
+      </c>
+      <c r="E114" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D115" s="1">
+        <v>1</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116" s="1">
+        <v>1</v>
+      </c>
+      <c r="E116" s="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D117" s="1">
+        <v>1</v>
+      </c>
+      <c r="E117" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D118" s="1">
+        <v>1</v>
+      </c>
+      <c r="E118" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D119" s="1">
+        <v>1</v>
+      </c>
+      <c r="E119" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D120" s="1">
+        <v>1</v>
+      </c>
+      <c r="E120" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D121" s="1">
+        <v>1</v>
+      </c>
+      <c r="E121" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D122" s="1">
+        <v>1</v>
+      </c>
+      <c r="E122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="1">
+        <v>1</v>
+      </c>
+      <c r="E123" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D124" s="1">
+        <v>1</v>
+      </c>
+      <c r="E124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D125" s="1">
+        <v>1</v>
+      </c>
+      <c r="E125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D126" s="1">
+        <v>1</v>
+      </c>
+      <c r="E126" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D127" s="1">
+        <v>1</v>
+      </c>
+      <c r="E127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D128" s="1">
+        <v>1</v>
+      </c>
+      <c r="E128" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D129" s="1">
+        <v>1</v>
+      </c>
+      <c r="E129" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D130" s="1">
+        <v>1</v>
+      </c>
+      <c r="E130" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D131" s="1">
+        <v>1</v>
+      </c>
+      <c r="E131" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D132" s="1">
+        <v>1</v>
+      </c>
+      <c r="E132" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D133" s="1">
+        <v>1</v>
+      </c>
+      <c r="E133" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D134" s="1">
+        <v>1</v>
+      </c>
+      <c r="E134" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D135" s="1">
+        <v>1</v>
+      </c>
+      <c r="E135" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A136" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D136" s="1">
+        <v>1</v>
+      </c>
+      <c r="E136" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D137" s="1">
+        <v>1</v>
+      </c>
+      <c r="E137" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A138" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D138" s="1">
+        <v>1</v>
+      </c>
+      <c r="E138" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D139" s="1">
+        <v>1</v>
+      </c>
+      <c r="E139" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D140" s="1">
+        <v>1</v>
+      </c>
+      <c r="E140" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D141" s="1">
+        <v>1</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D142" s="1">
+        <v>1</v>
+      </c>
+      <c r="E142" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D143" s="1">
+        <v>1</v>
+      </c>
+      <c r="E143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D144" s="1">
+        <v>1</v>
+      </c>
+      <c r="E144" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A145" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D145" s="1">
+        <v>1</v>
+      </c>
+      <c r="E145" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D146" s="1">
+        <v>1</v>
+      </c>
+      <c r="E146" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D147" s="1">
+        <v>1</v>
+      </c>
+      <c r="E147" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D148" s="1">
+        <v>1</v>
+      </c>
+      <c r="E148" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D149" s="1">
+        <v>1</v>
+      </c>
+      <c r="E149" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>67.78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1">
-        <v>74.44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="1">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="1">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1">
-        <v>96.67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="1">
-        <v>53.64</v>
+      <c r="B150" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D150" s="1">
+        <v>1</v>
+      </c>
+      <c r="E150" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D151" s="1">
+        <v>1</v>
+      </c>
+      <c r="E151" s="1">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -705,15 +3133,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -964,6 +3383,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -978,14 +3406,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AB7CB68-540E-4F04-820F-834558F23155}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1000,6 +3420,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Benchmarks.xlsx
+++ b/MAS_Benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935732B8-2D9D-4CF3-99F5-F70A618E6940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF641D5-8C35-4F91-BD9C-46DD618A918D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15180" yWindow="0" windowWidth="19280" windowHeight="13670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark_Data" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>Score</t>
   </si>
   <si>
-    <t>Tykee Walmsley</t>
-  </si>
-  <si>
     <t>February</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>Janruary</t>
+  </si>
+  <si>
+    <t>TyKee Walmsley</t>
   </si>
 </sst>
 </file>
@@ -160,16 +160,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -547,16 +544,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E151"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.453125" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" customWidth="1"/>
-    <col min="3" max="3" width="32.6328125" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -573,15 +570,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -590,15 +587,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -607,15 +604,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -624,15 +621,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -641,15 +638,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -658,15 +655,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -675,15 +672,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -692,15 +689,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -709,15 +706,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -726,15 +723,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -743,15 +740,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -760,15 +757,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
@@ -777,15 +774,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -794,15 +791,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -811,15 +808,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -828,15 +825,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -845,15 +842,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -862,15 +859,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
@@ -879,15 +876,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -896,15 +893,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -913,15 +910,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -930,15 +927,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -947,15 +944,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -964,15 +961,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -981,15 +978,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -998,15 +995,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -1015,15 +1012,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -1032,15 +1029,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -1049,15 +1046,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -1066,15 +1063,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
@@ -1083,15 +1080,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -1100,15 +1097,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
@@ -1117,15 +1114,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -1134,15 +1131,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -1151,15 +1148,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -1168,15 +1165,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
@@ -1185,15 +1182,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -1202,15 +1199,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -1219,15 +1216,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -1236,15 +1233,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -1253,15 +1250,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>14</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" s="1">
         <v>1</v>
@@ -1270,15 +1267,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
@@ -1287,15 +1284,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>14</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -1304,15 +1301,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
@@ -1321,15 +1318,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>14</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
@@ -1338,15 +1335,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>14</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -1355,15 +1352,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" s="1">
         <v>1</v>
@@ -1372,15 +1369,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>7</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
@@ -1389,15 +1386,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>7</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -1406,15 +1403,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D51" s="1">
         <v>1</v>
@@ -1423,15 +1420,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>7</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D52" s="1">
         <v>1</v>
@@ -1440,15 +1437,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -1457,15 +1454,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
@@ -1474,15 +1471,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
@@ -1491,15 +1488,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
@@ -1508,15 +1505,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>6</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D57" s="1">
         <v>1</v>
@@ -1525,15 +1522,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
@@ -1542,15 +1539,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -1559,15 +1556,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
@@ -1576,15 +1573,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D61" s="1">
         <v>1</v>
@@ -1593,15 +1590,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
@@ -1610,15 +1607,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
@@ -1627,15 +1624,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -1644,15 +1641,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>6</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -1661,15 +1658,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>6</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
@@ -1678,49 +1675,49 @@
         <v>90</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>21</v>
-      </c>
-      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>24</v>
       </c>
-      <c r="D67" s="1">
-        <v>1</v>
-      </c>
-      <c r="E67" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>21</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>24</v>
       </c>
-      <c r="D68" s="1">
-        <v>1</v>
-      </c>
-      <c r="E68" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>21</v>
-      </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
@@ -1729,15 +1726,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>21</v>
-      </c>
-      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70" s="1">
         <v>1</v>
@@ -1746,15 +1743,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -1763,15 +1760,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>21</v>
-      </c>
-      <c r="B72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
@@ -1780,15 +1777,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>21</v>
-      </c>
-      <c r="B73" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
@@ -1797,15 +1794,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -1814,15 +1811,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>16</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -1831,15 +1828,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>16</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -1848,15 +1845,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>16</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -1865,15 +1862,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>16</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D78" s="1">
         <v>1</v>
@@ -1882,15 +1879,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D79" s="1">
         <v>1</v>
@@ -1899,15 +1896,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>16</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
@@ -1916,15 +1913,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>16</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D81" s="1">
         <v>1</v>
@@ -1933,15 +1930,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>16</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D82" s="1">
         <v>1</v>
@@ -1950,15 +1947,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>16</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -1967,15 +1964,15 @@
         <v>98</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>16</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
@@ -1984,15 +1981,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>16</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D85" s="1">
         <v>1</v>
@@ -2001,15 +1998,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="4" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D86" s="1">
         <v>1</v>
@@ -2018,15 +2015,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="4" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D87" s="1">
         <v>1</v>
@@ -2035,15 +2032,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="4" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D88" s="1">
         <v>1</v>
@@ -2052,15 +2049,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="4" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D89" s="1">
         <v>1</v>
@@ -2069,15 +2066,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="4" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D90" s="1">
         <v>1</v>
@@ -2086,15 +2083,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="4" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -2103,15 +2100,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="4" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D92" s="1">
         <v>1</v>
@@ -2120,15 +2117,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="4" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D93" s="1">
         <v>1</v>
@@ -2137,15 +2134,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="4" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D94" s="1">
         <v>1</v>
@@ -2154,15 +2151,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="4" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
@@ -2171,15 +2168,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="4" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
@@ -2188,15 +2185,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="4" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D97" s="1">
         <v>1</v>
@@ -2205,15 +2202,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="4" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D98" s="1">
         <v>1</v>
@@ -2222,15 +2219,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" s="4" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D99" s="1">
         <v>1</v>
@@ -2239,15 +2236,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="4" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D100" s="1">
         <v>1</v>
@@ -2256,15 +2253,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="4" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D101" s="1">
         <v>1</v>
@@ -2273,15 +2270,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A102" s="4" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D102" s="1">
         <v>1</v>
@@ -2290,15 +2287,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A103" s="4" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D103" s="1">
         <v>1</v>
@@ -2307,15 +2304,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A104" s="4" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D104" s="1">
         <v>1</v>
@@ -2324,15 +2321,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105" s="4" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D105" s="1">
         <v>1</v>
@@ -2341,15 +2338,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="4" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D106" s="1">
         <v>1</v>
@@ -2358,15 +2355,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A107" s="4" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D107" s="1">
         <v>1</v>
@@ -2375,15 +2372,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A108" s="4" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D108" s="1">
         <v>1</v>
@@ -2392,15 +2389,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" s="4" t="s">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D109" s="1">
         <v>1</v>
@@ -2409,15 +2406,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110" s="4" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D110" s="1">
         <v>1</v>
@@ -2426,15 +2423,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" s="4" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D111" s="1">
         <v>1</v>
@@ -2443,15 +2440,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" s="4" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D112" s="1">
         <v>1</v>
@@ -2460,15 +2457,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A113" s="4" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D113" s="1">
         <v>1</v>
@@ -2477,15 +2474,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A114" s="4" t="s">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D114" s="1">
         <v>1</v>
@@ -2494,15 +2491,15 @@
         <v>90</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A115" s="4" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D115" s="1">
         <v>1</v>
@@ -2511,15 +2508,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A116" s="4" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D116" s="1">
         <v>1</v>
@@ -2528,15 +2525,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A117" s="4" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D117" s="1">
         <v>1</v>
@@ -2545,15 +2542,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A118" s="4" t="s">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D118" s="1">
         <v>1</v>
@@ -2562,15 +2559,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A119" s="4" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D119" s="1">
         <v>1</v>
@@ -2579,15 +2576,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A120" s="4" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D120" s="1">
         <v>1</v>
@@ -2596,15 +2593,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A121" s="4" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D121" s="1">
         <v>1</v>
@@ -2613,15 +2610,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A122" s="4" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D122" s="1">
         <v>1</v>
@@ -2630,15 +2627,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A123" s="4" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D123" s="1">
         <v>1</v>
@@ -2647,15 +2644,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A124" s="4" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D124" s="1">
         <v>1</v>
@@ -2664,15 +2661,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A125" s="4" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D125" s="1">
         <v>1</v>
@@ -2681,15 +2678,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A126" s="4" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D126" s="1">
         <v>1</v>
@@ -2698,15 +2695,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A127" s="4" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D127" s="1">
         <v>1</v>
@@ -2715,15 +2712,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128" s="4" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D128" s="1">
         <v>1</v>
@@ -2732,15 +2729,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" s="4" t="s">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D129" s="1">
         <v>1</v>
@@ -2749,15 +2746,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" s="4" t="s">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D130" s="1">
         <v>1</v>
@@ -2766,15 +2763,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" s="4" t="s">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D131" s="1">
         <v>1</v>
@@ -2783,15 +2780,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A132" s="4" t="s">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D132" s="1">
         <v>1</v>
@@ -2800,15 +2797,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" s="4" t="s">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D133" s="1">
         <v>1</v>
@@ -2817,15 +2814,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A134" s="4" t="s">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D134" s="1">
         <v>1</v>
@@ -2834,15 +2831,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A135" s="4" t="s">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D135" s="1">
         <v>1</v>
@@ -2851,15 +2848,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A136" s="4" t="s">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D136" s="1">
         <v>1</v>
@@ -2868,15 +2865,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A137" s="4" t="s">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D137" s="1">
         <v>1</v>
@@ -2885,15 +2882,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A138" s="4" t="s">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D138" s="1">
         <v>1</v>
@@ -2902,15 +2899,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A139" s="4" t="s">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D139" s="1">
         <v>1</v>
@@ -2919,15 +2916,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A140" s="4" t="s">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D140" s="1">
         <v>1</v>
@@ -2936,15 +2933,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A141" s="4" t="s">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D141" s="1">
         <v>1</v>
@@ -2953,15 +2950,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A142" s="4" t="s">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D142" s="1">
         <v>1</v>
@@ -2970,15 +2967,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A143" s="4" t="s">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D143" s="1">
         <v>1</v>
@@ -2987,15 +2984,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A144" s="4" t="s">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D144" s="1">
         <v>1</v>
@@ -3004,15 +3001,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A145" s="4" t="s">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D145" s="1">
         <v>1</v>
@@ -3021,15 +3018,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A146" s="4" t="s">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D146" s="1">
         <v>1</v>
@@ -3038,15 +3035,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A147" s="4" t="s">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D147" s="1">
         <v>1</v>
@@ -3055,15 +3052,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A148" s="4" t="s">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D148" s="1">
         <v>1</v>
@@ -3072,15 +3069,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A149" s="4" t="s">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D149" s="1">
         <v>1</v>
@@ -3089,15 +3086,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A150" s="4" t="s">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D150" s="1">
         <v>1</v>
@@ -3106,15 +3103,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A151" s="4" t="s">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D151" s="1">
         <v>1</v>
@@ -3133,6 +3130,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -3383,29 +3402,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AB7CB68-540E-4F04-820F-834558F23155}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3422,29 +3444,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/MAS_Benchmarks.xlsx
+++ b/MAS_Benchmarks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF641D5-8C35-4F91-BD9C-46DD618A918D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1378432E-27B7-46DE-8377-39B3087F1187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="880" windowWidth="27630" windowHeight="13520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Benchmark_Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="25">
   <si>
     <t>ManagerTeam</t>
   </si>
@@ -233,8 +233,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:E151" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E151" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}" name="tblBenchmarkData" displayName="tblBenchmarkData" ref="A1:E150" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E150" xr:uid="{71B9693B-4415-49D7-9582-118751D07E64}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{184B8945-C042-4F94-9625-44B9911492BE}" name="AssociateName" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{F39D70CE-E74D-40F2-80E4-9FA1AF055671}" name="ManagerTeam" dataDxfId="3"/>
@@ -543,17 +543,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E151"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E150"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.453125" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
@@ -570,7 +570,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -587,7 +587,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -621,7 +621,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -638,7 +638,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -672,7 +672,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -689,7 +689,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -706,7 +706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -723,7 +723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -740,7 +740,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -757,7 +757,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -791,7 +791,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -808,7 +808,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -825,7 +825,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -842,7 +842,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -859,7 +859,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -893,7 +893,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -910,7 +910,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -927,7 +927,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -944,7 +944,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -961,7 +961,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -978,7 +978,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -995,7 +995,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -1088,16 +1088,16 @@
         <v>1</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
       </c>
       <c r="E32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -1165,7 +1165,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -1179,27 +1179,27 @@
         <v>1</v>
       </c>
       <c r="E37" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
       </c>
       <c r="E38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -1247,10 +1247,10 @@
         <v>1</v>
       </c>
       <c r="E41" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -1264,10 +1264,10 @@
         <v>1</v>
       </c>
       <c r="E42" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -1281,10 +1281,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -1292,16 +1292,16 @@
         <v>1</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
       <c r="E44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -1315,10 +1315,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -1332,27 +1332,27 @@
         <v>1</v>
       </c>
       <c r="E46" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
       </c>
       <c r="E47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>7</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>7</v>
       </c>
@@ -1394,16 +1394,16 @@
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
       </c>
       <c r="E50" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -1417,10 +1417,10 @@
         <v>1</v>
       </c>
       <c r="E51" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -1434,10 +1434,10 @@
         <v>1</v>
       </c>
       <c r="E52" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>7</v>
       </c>
@@ -1451,10 +1451,10 @@
         <v>1</v>
       </c>
       <c r="E53" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D54" s="1">
         <v>1</v>
@@ -1471,7 +1471,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>7</v>
       </c>
@@ -1488,24 +1488,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D56" s="1">
         <v>1</v>
       </c>
       <c r="E56" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -1519,10 +1519,10 @@
         <v>1</v>
       </c>
       <c r="E57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1536,10 +1536,10 @@
         <v>1</v>
       </c>
       <c r="E58" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -1553,10 +1553,10 @@
         <v>1</v>
       </c>
       <c r="E59" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1587,10 +1587,10 @@
         <v>1</v>
       </c>
       <c r="E61" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -1641,7 +1641,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -1655,27 +1655,27 @@
         <v>1</v>
       </c>
       <c r="E65" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
       </c>
       <c r="E66" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>24</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>24</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>24</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>24</v>
       </c>
@@ -1768,16 +1768,16 @@
         <v>1</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>24</v>
       </c>
@@ -1791,18 +1791,18 @@
         <v>1</v>
       </c>
       <c r="E73" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -1811,7 +1811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>16</v>
       </c>
@@ -1825,10 +1825,10 @@
         <v>1</v>
       </c>
       <c r="E75" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>16</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>16</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D78" s="1">
         <v>1</v>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>16</v>
       </c>
@@ -1893,10 +1893,10 @@
         <v>1</v>
       </c>
       <c r="E79" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -1910,10 +1910,10 @@
         <v>1</v>
       </c>
       <c r="E80" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>16</v>
       </c>
@@ -1927,10 +1927,10 @@
         <v>1</v>
       </c>
       <c r="E81" s="1">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>16</v>
       </c>
@@ -1938,16 +1938,16 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D82" s="1">
         <v>1</v>
       </c>
       <c r="E82" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>16</v>
       </c>
@@ -1961,10 +1961,10 @@
         <v>1</v>
       </c>
       <c r="E83" s="1">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -1978,27 +1978,27 @@
         <v>1</v>
       </c>
       <c r="E84" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>16</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D85" s="1">
         <v>1</v>
       </c>
       <c r="E85" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="s">
         <v>9</v>
       </c>
@@ -2012,10 +2012,10 @@
         <v>1</v>
       </c>
       <c r="E86" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="s">
         <v>9</v>
       </c>
@@ -2029,10 +2029,10 @@
         <v>1</v>
       </c>
       <c r="E87" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>9</v>
       </c>
@@ -2046,10 +2046,10 @@
         <v>1</v>
       </c>
       <c r="E88" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>9</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="s">
         <v>9</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>9</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>2</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -2100,7 +2100,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>9</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>9</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>9</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>9</v>
       </c>
@@ -2168,24 +2168,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D96" s="1">
         <v>1</v>
       </c>
       <c r="E96" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>10</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="3" t="s">
         <v>10</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="3" t="s">
         <v>10</v>
       </c>
@@ -2233,10 +2233,10 @@
         <v>1</v>
       </c>
       <c r="E99" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="3" t="s">
         <v>10</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="3" t="s">
         <v>10</v>
       </c>
@@ -2267,10 +2267,10 @@
         <v>1</v>
       </c>
       <c r="E101" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="3" t="s">
         <v>10</v>
       </c>
@@ -2278,16 +2278,16 @@
         <v>2</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D102" s="1">
         <v>1</v>
       </c>
       <c r="E102" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>10</v>
       </c>
@@ -2301,10 +2301,10 @@
         <v>1</v>
       </c>
       <c r="E103" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="3" t="s">
         <v>10</v>
       </c>
@@ -2318,10 +2318,10 @@
         <v>1</v>
       </c>
       <c r="E104" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
         <v>10</v>
       </c>
@@ -2335,10 +2335,10 @@
         <v>1</v>
       </c>
       <c r="E105" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="3" t="s">
         <v>10</v>
       </c>
@@ -2352,27 +2352,27 @@
         <v>1</v>
       </c>
       <c r="E106" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D107" s="1">
         <v>1</v>
       </c>
       <c r="E107" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="3" t="s">
         <v>13</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
         <v>13</v>
       </c>
@@ -2403,10 +2403,10 @@
         <v>1</v>
       </c>
       <c r="E109" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>13</v>
       </c>
@@ -2420,10 +2420,10 @@
         <v>1</v>
       </c>
       <c r="E110" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>13</v>
       </c>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="E111" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>13</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>13</v>
       </c>
@@ -2465,16 +2465,16 @@
         <v>2</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D113" s="1">
         <v>1</v>
       </c>
       <c r="E113" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>13</v>
       </c>
@@ -2488,10 +2488,10 @@
         <v>1</v>
       </c>
       <c r="E114" s="1">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
         <v>13</v>
       </c>
@@ -2505,10 +2505,10 @@
         <v>1</v>
       </c>
       <c r="E115" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
         <v>13</v>
       </c>
@@ -2522,10 +2522,10 @@
         <v>1</v>
       </c>
       <c r="E116" s="1">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>13</v>
       </c>
@@ -2542,15 +2542,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D118" s="1">
         <v>1</v>
@@ -2559,7 +2559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>11</v>
       </c>
@@ -2573,10 +2573,10 @@
         <v>1</v>
       </c>
       <c r="E119" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
         <v>11</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="3" t="s">
         <v>11</v>
       </c>
@@ -2607,10 +2607,10 @@
         <v>1</v>
       </c>
       <c r="E121" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="3" t="s">
         <v>11</v>
       </c>
@@ -2624,10 +2624,10 @@
         <v>1</v>
       </c>
       <c r="E122" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="3" t="s">
         <v>11</v>
       </c>
@@ -2641,10 +2641,10 @@
         <v>1</v>
       </c>
       <c r="E123" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
         <v>11</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>2</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D124" s="1">
         <v>1</v>
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
         <v>11</v>
       </c>
@@ -2675,10 +2675,10 @@
         <v>1</v>
       </c>
       <c r="E125" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>11</v>
       </c>
@@ -2692,10 +2692,10 @@
         <v>1</v>
       </c>
       <c r="E126" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>11</v>
       </c>
@@ -2709,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="E127" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>11</v>
       </c>
@@ -2726,18 +2726,18 @@
         <v>1</v>
       </c>
       <c r="E128" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D129" s="1">
         <v>1</v>
@@ -2746,7 +2746,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>12</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>12</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>12</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>12</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>12</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>12</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>2</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D135" s="1">
         <v>1</v>
@@ -2848,7 +2848,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>12</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>12</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>12</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>12</v>
       </c>
@@ -2916,24 +2916,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D140" s="1">
         <v>1</v>
       </c>
       <c r="E140" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>15</v>
       </c>
@@ -2947,10 +2947,10 @@
         <v>1</v>
       </c>
       <c r="E141" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>15</v>
       </c>
@@ -2964,10 +2964,10 @@
         <v>1</v>
       </c>
       <c r="E142" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>15</v>
       </c>
@@ -2981,10 +2981,10 @@
         <v>1</v>
       </c>
       <c r="E143" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>15</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>15</v>
       </c>
@@ -3015,10 +3015,10 @@
         <v>1</v>
       </c>
       <c r="E145" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
         <v>15</v>
       </c>
@@ -3026,16 +3026,16 @@
         <v>2</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D146" s="1">
         <v>1</v>
       </c>
       <c r="E146" s="1">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
         <v>15</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
         <v>15</v>
       </c>
@@ -3066,10 +3066,10 @@
         <v>1</v>
       </c>
       <c r="E148" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="3" t="s">
         <v>15</v>
       </c>
@@ -3083,10 +3083,10 @@
         <v>1</v>
       </c>
       <c r="E149" s="1">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="3" t="s">
         <v>15</v>
       </c>
@@ -3100,23 +3100,6 @@
         <v>1</v>
       </c>
       <c r="E150" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D151" s="1">
-        <v>1</v>
-      </c>
-      <c r="E151" s="1">
         <v>100</v>
       </c>
     </row>
@@ -3130,6 +3113,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
@@ -3140,15 +3132,6 @@
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3403,6 +3386,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1678A2A8-E54E-4579-8501-27D3DA5E790E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -3415,14 +3406,6 @@
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F52CCA-3969-42A2-9F3F-81FB4D653F1D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
